--- a/preparedness/hurricane-kit/hurricane-inventory-tracker.xlsx
+++ b/preparedness/hurricane-kit/hurricane-inventory-tracker.xlsx
@@ -4685,7 +4685,7 @@
     <row r="50" ht="15" customHeight="1" s="37">
       <c r="B50" s="40" t="inlineStr">
         <is>
-          <t>Example row 7 is prefilled with sample values - overwrite it with your real numbers.</t>
+          <t>Example rows are blank. Enter your own quantities in the On hand column.</t>
         </is>
       </c>
       <c r="M50" s="70" t="inlineStr">
